--- a/public/templates/dmd-admin-orders.xlsx
+++ b/public/templates/dmd-admin-orders.xlsx
@@ -16,9 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
-    <t>Ngày tạo</t>
-  </si>
-  <si>
     <t>Sales</t>
   </si>
   <si>
@@ -40,7 +37,7 @@
     <t>Tracking</t>
   </si>
   <si>
-    <t>Order ID</t>
+    <t>Client Order ID</t>
   </si>
   <si>
     <t>Net Cost</t>
@@ -55,6 +52,9 @@
     <t>Discount</t>
   </si>
   <si>
+    <t>Lý do Discount</t>
+  </si>
+  <si>
     <t>Sales Price</t>
   </si>
   <si>
@@ -124,7 +124,7 @@
     <t>Điện thoại</t>
   </si>
   <si>
-    <t>RULE: Không đổi tên cột. Sales nên khớp Display Name hoặc Username của account đang Active.</t>
+    <t>RULE: Không đổi tên cột. Client Order ID là mã do khách cung cấp; DMD ID do hệ thống tự sinh. Ngày tạo do hệ thống tự lưu. Sales nên khớp Display Name hoặc Username đang Active.</t>
   </si>
 </sst>
 </file>
